--- a/uploads/subject_requirements.xlsx
+++ b/uploads/subject_requirements.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NITRO\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D0B612C-5C49-4E7E-889C-3DC71C997F66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F399CA9E-A21C-4ABD-9240-E279CE364F35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1500" yWindow="1500" windowWidth="17280" windowHeight="8880" xr2:uid="{23619E72-95E4-42DE-AF46-1D3CB9C6EB71}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{23619E72-95E4-42DE-AF46-1D3CB9C6EB71}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="44">
   <si>
     <t>class</t>
   </si>
@@ -75,22 +75,115 @@
     <t>CCW</t>
   </si>
   <si>
-    <t>N/W LAB</t>
-  </si>
-  <si>
-    <t>MINIPROJECT</t>
+    <t>S6_CSE_B</t>
+  </si>
+  <si>
+    <t>N/W LAB/MINI PROJECT</t>
+  </si>
+  <si>
+    <t>DMS</t>
+  </si>
+  <si>
+    <t>FOC</t>
+  </si>
+  <si>
+    <t>MAT-2</t>
+  </si>
+  <si>
+    <t>PHY</t>
+  </si>
+  <si>
+    <t>HW</t>
+  </si>
+  <si>
+    <t>CP/PHY LAB</t>
+  </si>
+  <si>
+    <t>CP</t>
+  </si>
+  <si>
+    <t>IPR</t>
+  </si>
+  <si>
+    <t>IT W/S/PHY LAB</t>
+  </si>
+  <si>
+    <t>LT</t>
+  </si>
+  <si>
+    <t>CP/IT W/S</t>
+  </si>
+  <si>
+    <t>S2_CSE_A</t>
+  </si>
+  <si>
+    <t>S2_CSE_B</t>
+  </si>
+  <si>
+    <t>S4_CSE_A</t>
+  </si>
+  <si>
+    <t>DBMS</t>
+  </si>
+  <si>
+    <t>OS</t>
+  </si>
+  <si>
+    <t>COA</t>
+  </si>
+  <si>
+    <t>SE</t>
+  </si>
+  <si>
+    <t>EESD</t>
+  </si>
+  <si>
+    <t>OS LAB/DBMS LAB</t>
+  </si>
+  <si>
+    <t>MAT-4</t>
+  </si>
+  <si>
+    <t>S4_CSE_B</t>
+  </si>
+  <si>
+    <t>S8_CSE</t>
+  </si>
+  <si>
+    <t>DC</t>
+  </si>
+  <si>
+    <t>CCV</t>
+  </si>
+  <si>
+    <t>NSP</t>
+  </si>
+  <si>
+    <t>PROJECT</t>
+  </si>
+  <si>
+    <t>CSA/DM</t>
+  </si>
+  <si>
+    <t>BCT/IOT</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -111,8 +204,9 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -120,8 +214,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{97B702D7-44DB-4241-BB12-5373F44DEED5}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -137,9 +232,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -177,7 +272,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -283,7 +378,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -425,7 +520,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -433,7 +528,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2AC3A33-A8CD-4725-822E-EC12DE8C587F}">
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D57"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.5546875" customWidth="1"/>
@@ -545,10 +640,10 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C8">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D8" t="s">
         <v>6</v>
@@ -556,54 +651,66 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C9">
+        <v>4</v>
+      </c>
+      <c r="D9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10">
+        <v>4</v>
+      </c>
+      <c r="D10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11">
+        <v>4</v>
+      </c>
+      <c r="D11" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12">
         <v>3</v>
       </c>
-      <c r="D9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10">
-        <v>4</v>
-      </c>
-      <c r="D10" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11">
-        <v>4</v>
-      </c>
-      <c r="D11" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12">
-        <v>4</v>
-      </c>
       <c r="D12" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
       <c r="B13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13">
         <v>3</v>
@@ -613,47 +720,619 @@
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
       <c r="B14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15">
+        <v>6</v>
+      </c>
+      <c r="D15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16">
+        <v>4</v>
+      </c>
+      <c r="D16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17">
+        <v>4</v>
+      </c>
+      <c r="D17" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18">
+        <v>4</v>
+      </c>
+      <c r="D18" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19">
+        <v>2</v>
+      </c>
+      <c r="D19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20">
+        <v>2</v>
+      </c>
+      <c r="D20" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21">
+        <v>2</v>
+      </c>
+      <c r="D21" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22">
+        <v>4</v>
+      </c>
+      <c r="D22" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" t="s">
+        <v>22</v>
+      </c>
+      <c r="C23">
         <v>3</v>
       </c>
-      <c r="D14" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B15" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15">
+      <c r="D23" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24">
+        <v>2</v>
+      </c>
+      <c r="D24" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25">
         <v>1</v>
       </c>
-      <c r="D15" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C16">
+      <c r="D25" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27">
+        <v>4</v>
+      </c>
+      <c r="D27" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28">
+        <v>4</v>
+      </c>
+      <c r="D28" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>27</v>
+      </c>
+      <c r="B29" t="s">
+        <v>17</v>
+      </c>
+      <c r="C29">
+        <v>4</v>
+      </c>
+      <c r="D29" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>27</v>
+      </c>
+      <c r="B30" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30">
+        <v>2</v>
+      </c>
+      <c r="D30" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>27</v>
+      </c>
+      <c r="B31" t="s">
+        <v>19</v>
+      </c>
+      <c r="C31">
+        <v>2</v>
+      </c>
+      <c r="D31" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>27</v>
+      </c>
+      <c r="B32" t="s">
+        <v>20</v>
+      </c>
+      <c r="C32">
+        <v>2</v>
+      </c>
+      <c r="D32" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>27</v>
+      </c>
+      <c r="B33" t="s">
+        <v>21</v>
+      </c>
+      <c r="C33">
+        <v>4</v>
+      </c>
+      <c r="D33" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>27</v>
+      </c>
+      <c r="B34" t="s">
+        <v>22</v>
+      </c>
+      <c r="C34">
         <v>3</v>
       </c>
-      <c r="D16" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B17" t="s">
+      <c r="D34" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>27</v>
+      </c>
+      <c r="B35" t="s">
+        <v>23</v>
+      </c>
+      <c r="C35">
+        <v>2</v>
+      </c>
+      <c r="D35" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>27</v>
+      </c>
+      <c r="B36" t="s">
+        <v>24</v>
+      </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
+      <c r="D36" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>27</v>
+      </c>
+      <c r="B37" t="s">
+        <v>25</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+      <c r="D37" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>28</v>
+      </c>
+      <c r="B38" t="s">
+        <v>35</v>
+      </c>
+      <c r="C38">
+        <v>4</v>
+      </c>
+      <c r="D38" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>28</v>
+      </c>
+      <c r="B39" t="s">
+        <v>29</v>
+      </c>
+      <c r="C39">
+        <v>6</v>
+      </c>
+      <c r="D39" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>28</v>
+      </c>
+      <c r="B40" t="s">
+        <v>30</v>
+      </c>
+      <c r="C40">
+        <v>6</v>
+      </c>
+      <c r="D40" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>28</v>
+      </c>
+      <c r="B41" t="s">
+        <v>31</v>
+      </c>
+      <c r="C41">
+        <v>6</v>
+      </c>
+      <c r="D41" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>28</v>
+      </c>
+      <c r="B42" t="s">
+        <v>32</v>
+      </c>
+      <c r="C42">
+        <v>5</v>
+      </c>
+      <c r="D42" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>28</v>
+      </c>
+      <c r="B43" t="s">
+        <v>33</v>
+      </c>
+      <c r="C43">
+        <v>2</v>
+      </c>
+      <c r="D43" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>28</v>
+      </c>
+      <c r="B44" t="s">
+        <v>34</v>
+      </c>
+      <c r="C44">
+        <v>6</v>
+      </c>
+      <c r="D44" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>36</v>
+      </c>
+      <c r="B45" t="s">
+        <v>35</v>
+      </c>
+      <c r="C45">
+        <v>4</v>
+      </c>
+      <c r="D45" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>36</v>
+      </c>
+      <c r="B46" t="s">
+        <v>29</v>
+      </c>
+      <c r="C46">
+        <v>6</v>
+      </c>
+      <c r="D46" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>36</v>
+      </c>
+      <c r="B47" t="s">
+        <v>30</v>
+      </c>
+      <c r="C47">
+        <v>6</v>
+      </c>
+      <c r="D47" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>36</v>
+      </c>
+      <c r="B48" t="s">
+        <v>31</v>
+      </c>
+      <c r="C48">
+        <v>6</v>
+      </c>
+      <c r="D48" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>36</v>
+      </c>
+      <c r="B49" t="s">
+        <v>32</v>
+      </c>
+      <c r="C49">
+        <v>5</v>
+      </c>
+      <c r="D49" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>36</v>
+      </c>
+      <c r="B50" t="s">
+        <v>33</v>
+      </c>
+      <c r="C50">
+        <v>2</v>
+      </c>
+      <c r="D50" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>36</v>
+      </c>
+      <c r="B51" t="s">
+        <v>34</v>
+      </c>
+      <c r="C51">
+        <v>6</v>
+      </c>
+      <c r="D51" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>37</v>
+      </c>
+      <c r="B52" t="s">
+        <v>38</v>
+      </c>
+      <c r="C52">
+        <v>5</v>
+      </c>
+      <c r="D52" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>37</v>
+      </c>
+      <c r="B53" t="s">
+        <v>39</v>
+      </c>
+      <c r="C53">
+        <v>2</v>
+      </c>
+      <c r="D53" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>37</v>
+      </c>
+      <c r="B54" t="s">
+        <v>40</v>
+      </c>
+      <c r="C54">
+        <v>5</v>
+      </c>
+      <c r="D54" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>37</v>
+      </c>
+      <c r="B55" t="s">
+        <v>42</v>
+      </c>
+      <c r="C55">
+        <v>5</v>
+      </c>
+      <c r="D55" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>37</v>
+      </c>
+      <c r="B56" t="s">
+        <v>41</v>
+      </c>
+      <c r="C56">
         <v>14</v>
       </c>
-      <c r="C17">
-        <v>3</v>
-      </c>
-      <c r="D17" t="s">
-        <v>6</v>
+      <c r="D56" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>37</v>
+      </c>
+      <c r="B57" t="s">
+        <v>43</v>
+      </c>
+      <c r="C57">
+        <v>5</v>
+      </c>
+      <c r="D57" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
